--- a/lessons/codex-ai-video-workshop/materials/reference-results/01-invoice/invoice-register.xlsx
+++ b/lessons/codex-ai-video-workshop/materials/reference-results/01-invoice/invoice-register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" r:id="R2984be3e5e20409f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="2" r:id="R47ccb28fac3b4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" r:id="Rebb1bb2bca6c4d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="2" r:id="Rd5ff1398ec2845cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,24 +14,45 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  <x:numFmts count="4">
+    <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
+    <x:numFmt numFmtId="202" formatCode="0%"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:color rgb="FF1F1B2D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFEF7"/>
       <x:name val="Arial"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FFFFFEF7"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFEF7"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFEF7"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -44,7 +65,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17142A"/>
+        <x:fgColor rgb="FF1F1B2D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -60,23 +81,42 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -280,352 +320,514 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="60" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="43" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>source_file</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>source_page</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>vendor</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>invoice_number</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>invoice_date</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>due_date</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="str">
-        <x:v>purchase_order</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="I1" s="4" t="str">
-        <x:v>subtotal</x:v>
-      </x:c>
-      <x:c r="J1" s="4" t="str">
-        <x:v>tax_as_stated</x:v>
-      </x:c>
-      <x:c r="K1" s="4" t="str">
-        <x:v>total_as_stated</x:v>
-      </x:c>
-      <x:c r="L1" s="4" t="str">
-        <x:v>calculated_total</x:v>
-      </x:c>
-      <x:c r="M1" s="4" t="str">
-        <x:v>difference</x:v>
-      </x:c>
-      <x:c r="N1" s="4" t="str">
-        <x:v>status</x:v>
-      </x:c>
-      <x:c r="O1" s="4" t="str">
-        <x:v>reason</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="2" t="str">
+    <x:row r="1" ht="48" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Source file</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>Page</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>Supplier</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="str">
+        <x:v>Supplier ABN</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="str">
+        <x:v>Buyer</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="str">
+        <x:v>Document type</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="str">
+        <x:v>Invoice number</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="str">
+        <x:v>Issue date</x:v>
+      </x:c>
+      <x:c r="I1" s="5" t="str">
+        <x:v>Due date</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="str">
+        <x:v>Purchase order</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="str">
+        <x:v>Currency</x:v>
+      </x:c>
+      <x:c r="L1" s="5" t="str">
+        <x:v>Subtotal ex GST</x:v>
+      </x:c>
+      <x:c r="M1" s="5" t="str">
+        <x:v>GST rate</x:v>
+      </x:c>
+      <x:c r="N1" s="5" t="str">
+        <x:v>GST shown</x:v>
+      </x:c>
+      <x:c r="O1" s="5" t="str">
+        <x:v>Total incl GST</x:v>
+      </x:c>
+      <x:c r="P1" s="5" t="str">
+        <x:v>Calculated GST</x:v>
+      </x:c>
+      <x:c r="Q1" s="5" t="str">
+        <x:v>Calculated total</x:v>
+      </x:c>
+      <x:c r="R1" s="5" t="str">
+        <x:v>Amount difference</x:v>
+      </x:c>
+      <x:c r="S1" s="5" t="str">
+        <x:v>Duplicate check</x:v>
+      </x:c>
+      <x:c r="T1" s="5" t="str">
+        <x:v>GST-credit review</x:v>
+      </x:c>
+      <x:c r="U1" s="5" t="str">
+        <x:v>GST difference</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="6" t="str">
         <x:v>01-lumen.pdf</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="n">
+      <x:c r="B2" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="str">
-        <x:v>Lumen Event Studio (Fictional)</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="str">
+      <x:c r="C2" s="6" t="str">
+        <x:v>Lumen Event Studio</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>80 000 000 001</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
         <x:v>LUM-1001</x:v>
       </x:c>
-      <x:c r="E2" s="5" t="d">
+      <x:c r="H2" s="7" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F2" s="5" t="d">
+      <x:c r="I2" s="7" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="str">
+      <x:c r="J2" s="6" t="str">
         <x:v>EV-026</x:v>
       </x:c>
-      <x:c r="H2" s="2" t="str">
+      <x:c r="K2" s="6" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="n">
+      <x:c r="L2" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="J2" s="6" t="n">
+      <x:c r="M2" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N2" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K2" s="6" t="n">
+      <x:c r="O2" s="8" t="n">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="L2" s="6" t="n">
-        <x:f>I2+J2</x:f>
+      <x:c r="P2" s="8" t="n">
+        <x:f>ROUND(L2*M2,2)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="n">
+        <x:f>ROUND(L2+N2,2)</x:f>
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="M2" s="6" t="n">
-        <x:f>K2-L2</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="2" t="str">
-        <x:v>Recorded</x:v>
-      </x:c>
-      <x:c r="O2" s="2" t="str"/>
-    </x:row>
-    <x:row r="3" ht="27" customHeight="1">
-      <x:c r="A3" s="2" t="str">
+      <x:c r="R2" s="8" t="n">
+        <x:f>ROUND(O2-Q2,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C2,C2,$G$2:G2,G2,$K$2:K2,K2)&gt;1,"Duplicate","Unique")</x:f>
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="T2" s="6" t="str">
+        <x:f>IF(D2="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U2" s="10" t="n">
+        <x:f>ROUND(N2-P2,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="6" t="str">
         <x:v>02-harbour.pdf</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="n">
+      <x:c r="B3" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="str">
-        <x:v>Harbour Print Lab (Fictional)</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="str">
+      <x:c r="C3" s="6" t="str">
+        <x:v>Harbour Print Lab</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>61 000 000 002</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
         <x:v>HPL-2008</x:v>
       </x:c>
-      <x:c r="E3" s="5" t="d">
+      <x:c r="H3" s="7" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F3" s="5" t="d">
+      <x:c r="I3" s="7" t="d">
         <x:v>2026-10-17T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="str">
+      <x:c r="J3" s="6" t="str">
         <x:v>EV-026</x:v>
       </x:c>
-      <x:c r="H3" s="2" t="str">
+      <x:c r="K3" s="6" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="I3" s="6" t="n">
+      <x:c r="L3" s="8" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="J3" s="6" t="n">
+      <x:c r="M3" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N3" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K3" s="6" t="n">
+      <x:c r="O3" s="8" t="n">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="L3" s="6" t="n">
-        <x:f>I3+J3</x:f>
+      <x:c r="P3" s="8" t="n">
+        <x:f>ROUND(L3*M3,2)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q3" s="8" t="n">
+        <x:f>ROUND(L3+N3,2)</x:f>
         <x:v>660</x:v>
       </x:c>
-      <x:c r="M3" s="6" t="n">
-        <x:f>K3-L3</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="2" t="str">
-        <x:v>Recorded</x:v>
-      </x:c>
-      <x:c r="O3" s="2" t="str"/>
-    </x:row>
-    <x:row r="4" ht="27" customHeight="1">
-      <x:c r="A4" s="2" t="str">
+      <x:c r="R3" s="8" t="n">
+        <x:f>ROUND(O3-Q3,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C3,C3,$G$2:G3,G3,$K$2:K3,K3)&gt;1,"Duplicate","Unique")</x:f>
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="T3" s="6" t="str">
+        <x:f>IF(D3="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U3" s="10" t="n">
+        <x:f>ROUND(N3-P3,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="6" t="str">
         <x:v>03-north.pdf</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="n">
+      <x:c r="B4" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>North Desk Supplies (Fictional)</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="str">
+      <x:c r="C4" s="6" t="str">
+        <x:v>North Desk Supplies</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>42 000 000 003</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
         <x:v>NDS-0032</x:v>
       </x:c>
-      <x:c r="E4" s="5" t="d">
+      <x:c r="H4" s="7" t="d">
         <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F4" s="5"/>
-      <x:c r="G4" s="2"/>
-      <x:c r="H4" s="2" t="str">
+      <x:c r="I4" s="7"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="I4" s="6" t="n">
+      <x:c r="L4" s="8" t="n">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="J4" s="6" t="n">
+      <x:c r="M4" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N4" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K4" s="6" t="n">
+      <x:c r="O4" s="8" t="n">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="L4" s="6" t="n">
-        <x:f>I4+J4</x:f>
+      <x:c r="P4" s="8" t="n">
+        <x:f>ROUND(L4*M4,2)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q4" s="8" t="n">
+        <x:f>ROUND(L4+N4,2)</x:f>
         <x:v>275</x:v>
       </x:c>
-      <x:c r="M4" s="6" t="n">
-        <x:f>K4-L4</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="2" t="str">
-        <x:v>Missing fields</x:v>
-      </x:c>
-      <x:c r="O4" s="2" t="str">
-        <x:v>Due date and purchase order not provided</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="27" customHeight="1">
-      <x:c r="A5" s="2" t="str">
+      <x:c r="R4" s="8" t="n">
+        <x:f>ROUND(O4-Q4,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S4" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C4,C4,$G$2:G4,G4,$K$2:K4,K4)&gt;1,"Duplicate","Unique")</x:f>
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="T4" s="6" t="str">
+        <x:f>IF(D4="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U4" s="10" t="n">
+        <x:f>ROUND(N4-P4,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="6" t="str">
         <x:v>04-cloud.pdf</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="n">
+      <x:c r="B5" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="str">
-        <x:v>Cloud Clip Library (Fictional)</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="str">
+      <x:c r="C5" s="6" t="str">
+        <x:v>Cloud Clip Library</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>23 000 000 004</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
         <x:v>CCL-0410</x:v>
       </x:c>
-      <x:c r="E5" s="5" t="d">
+      <x:c r="H5" s="7" t="d">
         <x:v>2026-10-07T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="d">
+      <x:c r="I5" s="7" t="d">
         <x:v>2026-10-21T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G5" s="2" t="str">
+      <x:c r="J5" s="6" t="str">
         <x:v>MEDIA-04</x:v>
       </x:c>
-      <x:c r="H5" s="2" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I5" s="6" t="n">
+      <x:c r="K5" s="6" t="str">
+        <x:v>AUD</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="J5" s="6" t="n">
+      <x:c r="M5" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N5" s="8" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K5" s="6" t="n">
+      <x:c r="O5" s="8" t="n">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="L5" s="6" t="n">
-        <x:f>I5+J5</x:f>
+      <x:c r="P5" s="8" t="n">
+        <x:f>ROUND(L5*M5,2)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q5" s="8" t="n">
+        <x:f>ROUND(L5+N5,2)</x:f>
         <x:v>330</x:v>
       </x:c>
-      <x:c r="M5" s="6" t="n">
-        <x:f>K5-L5</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="2" t="str">
-        <x:v>Recorded</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="str"/>
-    </x:row>
-    <x:row r="6" ht="27" customHeight="1">
-      <x:c r="A6" s="2" t="str">
+      <x:c r="R5" s="8" t="n">
+        <x:f>ROUND(O5-Q5,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C5,C5,$G$2:G5,G5,$K$2:K5,K5)&gt;1,"Duplicate","Unique")</x:f>
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="T5" s="6" t="str">
+        <x:f>IF(D5="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U5" s="10" t="n">
+        <x:f>ROUND(N5-P5,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="6" t="str">
         <x:v>05-stage.pdf</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="n">
+      <x:c r="B6" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>Stage Kit Hire (Fictional)</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="str">
+      <x:c r="C6" s="6" t="str">
+        <x:v>Stage Kit Hire</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>93 000 000 005</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
         <x:v>SKH-0501</x:v>
       </x:c>
-      <x:c r="E6" s="5" t="d">
+      <x:c r="H6" s="7" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F6" s="5" t="d">
+      <x:c r="I6" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G6" s="2" t="str">
+      <x:c r="J6" s="6" t="str">
         <x:v>EV-026</x:v>
       </x:c>
-      <x:c r="H6" s="2" t="str">
+      <x:c r="K6" s="6" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="I6" s="6" t="n">
+      <x:c r="L6" s="8" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="J6" s="6" t="n">
+      <x:c r="M6" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K6" s="6" t="n">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="L6" s="6" t="n">
-        <x:f>I6+J6</x:f>
+      <x:c r="O6" s="8" t="n">
         <x:v>550</x:v>
       </x:c>
-      <x:c r="M6" s="6" t="n">
-        <x:f>K6-L6</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N6" s="2" t="str">
-        <x:v>Arithmetic discrepancy</x:v>
-      </x:c>
-      <x:c r="O6" s="2" t="str">
-        <x:v>Stated total exceeds subtotal plus tax by 10 AUD</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="27" customHeight="1">
-      <x:c r="A7" s="2" t="str">
+      <x:c r="P6" s="8" t="n">
+        <x:f>ROUND(L6*M6,2)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="n">
+        <x:f>ROUND(L6+N6,2)</x:f>
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="R6" s="8" t="n">
+        <x:f>ROUND(O6-Q6,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C6,C6,$G$2:G6,G6,$K$2:K6,K6)&gt;1,"Duplicate","Unique")</x:f>
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="T6" s="6" t="str">
+        <x:f>IF(D6="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U6" s="10" t="n">
+        <x:f>ROUND(N6-P6,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="6" t="str">
         <x:v>06-lumen-copy.pdf</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="n">
+      <x:c r="B7" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>Lumen Event Studio (Fictional)</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="str">
+      <x:c r="C7" s="6" t="str">
+        <x:v>Lumen Event Studio</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>80 000 000 001</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>Cedar Events</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>TAX INVOICE</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
         <x:v>LUM-1001</x:v>
       </x:c>
-      <x:c r="E7" s="5" t="d">
+      <x:c r="H7" s="7" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="F7" s="5" t="d">
+      <x:c r="I7" s="7" t="d">
         <x:v>2026-10-15T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G7" s="2" t="str">
+      <x:c r="J7" s="6" t="str">
         <x:v>EV-026</x:v>
       </x:c>
-      <x:c r="H7" s="2" t="str">
+      <x:c r="K7" s="6" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="I7" s="6" t="n">
+      <x:c r="L7" s="8" t="n">
         <x:v>1000</x:v>
       </x:c>
-      <x:c r="J7" s="6" t="n">
+      <x:c r="M7" s="9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N7" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K7" s="6" t="n">
+      <x:c r="O7" s="8" t="n">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="L7" s="6" t="n">
-        <x:f>I7+J7</x:f>
+      <x:c r="P7" s="8" t="n">
+        <x:f>ROUND(L7*M7,2)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="n">
+        <x:f>ROUND(L7+N7,2)</x:f>
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="M7" s="6" t="n">
-        <x:f>K7-L7</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="2" t="str">
+      <x:c r="R7" s="8" t="n">
+        <x:f>ROUND(O7-Q7,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="6" t="str">
+        <x:f>IF(COUNTIFS($C$2:C7,C7,$G$2:G7,G7,$K$2:K7,K7)&gt;1,"Duplicate","Unique")</x:f>
         <x:v>Duplicate</x:v>
       </x:c>
-      <x:c r="O7" s="2" t="str">
-        <x:v>Same key as 01-lumen.pdf</x:v>
+      <x:c r="T7" s="6" t="str">
+        <x:f>IF(D7="","Supplier ABN missing; verify before claiming","ABR no record; verify before claiming")</x:f>
+        <x:v>ABR no record; verify before claiming</x:v>
+      </x:c>
+      <x:c r="U7" s="10" t="n">
+        <x:f>ROUND(N7-P7,2)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -637,46 +839,127 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Currency</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>Unique stated total</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Excluding arithmetic discrepancy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="2" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>Australian invoice review</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>Unit / review</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="16" t="str">
+        <x:v>Source documents</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="n">
+        <x:f>COUNTA(Register!A2:A7)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>files</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>Unique invoices</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="n">
+        <x:f>COUNTIF(Register!S2:S7,"Unique")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="16" t="str">
+        <x:v>invoices</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>Duplicate originals</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="n">
+        <x:f>COUNTIF(Register!S2:S7,"Duplicate")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>files</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>Subtotal ex GST</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="n">
+        <x:f>SUMIFS(Register!L2:L7,Register!S2:S7,"Unique")</x:f>
+        <x:v>2650</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
         <x:v>AUD</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="n">
-        <x:f>SUMIFS(Register!$K$2:$K$7,Register!$H$2:$H$7,A2,Register!$N$2:$N$7,"&lt;&gt;Duplicate")</x:f>
-        <x:v>2595</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="n">
-        <x:f>SUMIFS(Register!$K$2:$K$7,Register!$H$2:$H$7,A2,Register!$N$2:$N$7,"&lt;&gt;Duplicate",Register!$M$2:$M$7,0)</x:f>
-        <x:v>2035</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="27" customHeight="1">
-      <x:c r="A3" s="2" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="n">
-        <x:f>SUMIFS(Register!$K$2:$K$7,Register!$H$2:$H$7,A3,Register!$N$2:$N$7,"&lt;&gt;Duplicate")</x:f>
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="n">
-        <x:f>SUMIFS(Register!$K$2:$K$7,Register!$H$2:$H$7,A3,Register!$N$2:$N$7,"&lt;&gt;Duplicate",Register!$M$2:$M$7,0)</x:f>
-        <x:v>330</x:v>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>GST shown</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="n">
+        <x:f>SUMIFS(Register!N2:N7,Register!S2:S7,"Unique")</x:f>
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>AUD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>Total incl GST</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="n">
+        <x:f>SUMIFS(Register!O2:O7,Register!S2:S7,"Unique")</x:f>
+        <x:v>2915</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>AUD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>Arithmetic exceptions</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="n">
+        <x:f>COUNTIFS(Register!R2:R7,"&lt;&gt;0",Register!S2:S7,"Unique")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="str">
+        <x:v>unique invoices</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>ABR no-record results</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="n">
+        <x:f>COUNTIFS(Register!T2:T7,"ABR no record; verify before claiming",Register!S2:S7,"Unique")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>unique invoices</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>GST-credit eligibility</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>Not determined</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>Supplier identity and GST registration require verification</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
